--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T08:17:27+00:00</t>
+    <t>2023-11-21T14:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T14:08:22+00:00</t>
+    <t>2023-11-21T15:06:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T15:06:57+00:00</t>
+    <t>2023-11-21T15:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T15:46:53+00:00</t>
+    <t>2023-11-21T16:01:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T16:01:46+00:00</t>
+    <t>2023-11-21T16:06:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T16:06:52+00:00</t>
+    <t>2023-11-22T15:35:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T15:35:46+00:00</t>
+    <t>2023-11-22T15:45:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T15:45:36+00:00</t>
+    <t>2023-11-22T15:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T15:47:55+00:00</t>
+    <t>2023-11-22T16:02:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T16:02:35+00:00</t>
+    <t>2023-11-22T16:24:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T16:24:01+00:00</t>
+    <t>2023-11-24T09:28:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-24T09:28:27+00:00</t>
+    <t>2023-11-29T07:54:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T07:54:05+00:00</t>
+    <t>2023-12-13T14:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/all-profiles.xlsx
+++ b/ig/epd/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T14:14:48+00:00</t>
+    <t>2023-12-13T15:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1291,7 +1291,7 @@
  TRE_A04-TypeDocument-LOINC, OID : 2.16.840.1.113883.6.1
  TRE_A12-NomenclatureASTM, OID : ASTM
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J66-TypeCode-DMP).
-En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J07-XdsTypeCode-CISIS peut être utilisé. {f:type}</t>
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J07-XdsTypeCode-CISIS peut être utilisé. {null}</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -1318,7 +1318,7 @@
 -	TRE_A03-ClasseDocument-CISIS, OID : 1.2.250.1.213.1.1.4.1
 -	TRE_A10-NomenclatureURN, OID : URN
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J57-ClassCode-DMP).
-En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J06-XdsClassCode-CISIS peut être utilisé. {f:category}</t>
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J06-XdsClassCode-CISIS peut être utilisé. {null}</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>
@@ -1489,7 +1489,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-bind-securityLabel:Les codes pour cet élément doivent provenir du ValueSet spécifié par le standard. Lorsqu’aucun code ne correspond au concept recherché, un code provenant de la terminologie de référence TRE_A07-StatusVisibiliteDocument, OID : 1.2.250.1.213.1.1.4.13 peut être utilisé. {f:securityLabel}</t>
+constr-bind-securityLabel:Les codes pour cet élément doivent provenir du ValueSet spécifié par le standard. Lorsqu’aucun code ne correspond au concept recherché, un code provenant de la terminologie de référence TRE_A07-StatusVisibiliteDocument, OID : 1.2.250.1.213.1.1.4.13 peut être utilisé. {null}</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -1720,7 +1720,7 @@
 - TRE_A09-DICOMuidRegistry, OID : 1.2.840.10008.2.6.1
 - TRE_A10-NomenclatureURN, OID : URN
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J60-FormatCode-DMP).
-En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J10-XdsFormatCode-CISIS peut être utilisé. {f:content/f:format}</t>
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J10-XdsFormatCode-CISIS peut être utilisé. {null}</t>
   </si>
   <si>
     <t>DocumentReference.context</t>
@@ -1779,7 +1779,7 @@
 constr-bind-context-event:Nomenclatures utilisées :
 - CCAM pour les actes médicaux (OID="1.2.250.1.213.2.5");
 - CIM-10 pour les diagnostics de pathologie (OID="2.16.840.1.113883.6.3").
-- TRE_A00-ProducteurDocNonPS pour les documents d'expression personnelle du patient. {f:context/f:event}</t>
+- TRE_A00-ProducteurDocNonPS pour les documents d'expression personnelle du patient. {null}</t>
   </si>
   <si>
     <t>DocumentReference.context.period</t>
@@ -1822,7 +1822,7 @@
 constr-bind-ProducteurDoc-simplified:L’utilisation de cette nomenclature est recommandée mais non obligatoire (prefered) :
 -	TRE_R02-SecteurActivite, OID : 1.2.250.1.71.4.2.4 (lorsque l’auteur du document est un professionnel ou un équipement sous sa responsabilité)
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J61-HealthcareFacilityTypeCode-DMP).
-En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J02-XdsHealthcareFacilityTypeCode-CISIS peut être utilisé. {f:context/f:practiceSetting or f:context/f:facilityType}</t>
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J02-XdsHealthcareFacilityTypeCode-CISIS peut être utilisé. {null}</t>
   </si>
   <si>
     <t>DocumentReference.context.practiceSetting</t>
@@ -7434,7 +7434,7 @@
         <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>75</v>
